--- a/basedatos_partidas/salida/descompuestos/05.04.01.060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/05.04.01.060.xlsx
@@ -584,7 +584,7 @@
         <v>0.02</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
